--- a/templates/reports/약품관리대장.xlsx
+++ b/templates/reports/약품관리대장.xlsx
@@ -1,35 +1,217 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <workbookPr defaultThemeVersion="202300"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\OneDrive\바탕 화면\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96A64CCF-9A96-414A-8424-39EF87065434}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="28680" yWindow="-5970" windowWidth="29040" windowHeight="15720" xr2:uid="{524B5CD6-E898-41CC-B8D2-EA6C60426A48}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="템플릿" state="visible" r:id="rId4"/>
+    <sheet name="약품" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">약품!$A$1:$E$20</definedName>
+    <definedName name="대장명">약품!$A$1</definedName>
+    <definedName name="사용약품">약품!$A$3</definedName>
+    <definedName name="알칼리구매">약품!$B$18</definedName>
+    <definedName name="알칼리누계">약품!$D$18</definedName>
+    <definedName name="알칼리사용">약품!$C$18</definedName>
+    <definedName name="알칼리잔량">약품!$E$18</definedName>
+    <definedName name="암모니아구매">약품!$B$15</definedName>
+    <definedName name="암모니아누계">약품!$D$15</definedName>
+    <definedName name="암모니아사용">약품!$C$15</definedName>
+    <definedName name="암모니아잔량">약품!$E$15</definedName>
+    <definedName name="약1구매">약품!$B$5</definedName>
+    <definedName name="약1누계">약품!$D$5</definedName>
+    <definedName name="약1사용">약품!$C$5</definedName>
+    <definedName name="약1잔량">약품!$E$5</definedName>
+    <definedName name="약2구매">약품!$B$6</definedName>
+    <definedName name="약2누계">약품!$D$6</definedName>
+    <definedName name="약2사용">약품!$C$6</definedName>
+    <definedName name="약2잔량">약품!$E$6</definedName>
+    <definedName name="약3구매">약품!$B$7</definedName>
+    <definedName name="약3누계">약품!$D$7</definedName>
+    <definedName name="약3사용">약품!$C$7</definedName>
+    <definedName name="약3잔량">약품!$E$7</definedName>
+    <definedName name="인구매">약품!$B$17</definedName>
+    <definedName name="인누계">약품!$D$17</definedName>
+    <definedName name="인사용">약품!$C$17</definedName>
+    <definedName name="인잔량">약품!$E$17</definedName>
+    <definedName name="질산구매">약품!$B$16</definedName>
+    <definedName name="질산누계">약품!$D$16</definedName>
+    <definedName name="질산사용">약품!$C$16</definedName>
+    <definedName name="질산잔량">약품!$E$16</definedName>
+    <definedName name="추1구매">약품!$B$8</definedName>
+    <definedName name="추1누계">약품!$D$8</definedName>
+    <definedName name="추1사용">약품!$C$8</definedName>
+    <definedName name="추1약품명">약품!$A$8</definedName>
+    <definedName name="추1잔량">약품!$E$8</definedName>
+    <definedName name="추2구매">약품!$B$9</definedName>
+    <definedName name="추2누계">약품!$D$9</definedName>
+    <definedName name="추2사용">약품!$C$9</definedName>
+    <definedName name="추2약품명">약품!$A$9</definedName>
+    <definedName name="추2잔량">약품!$E$9</definedName>
+    <definedName name="추3구매">약품!$B$10</definedName>
+    <definedName name="추3누계">약품!$D$10</definedName>
+    <definedName name="추3사용">약품!$C$10</definedName>
+    <definedName name="추3약품명">약품!$A$10</definedName>
+    <definedName name="추3잔량">약품!$E$10</definedName>
+    <definedName name="현장명">약품!$A$2</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
-  <si>
-    <t>약품관리대장 기본 템플릿</t>
-  </si>
-  <si>
-    <t>이 파일은 기본 번들 템플릿입니다. 실제 양식은 필요에 따라 교체해주세요.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+  <si>
+    <t>품 명</t>
+  </si>
+  <si>
+    <t>구 입 량</t>
+  </si>
+  <si>
+    <t>사 용 량</t>
+  </si>
+  <si>
+    <t>누 계</t>
+  </si>
+  <si>
+    <t>잔 량</t>
+  </si>
+  <si>
+    <t>포 도 당</t>
+  </si>
+  <si>
+    <t>중탄산나트륨</t>
+  </si>
+  <si>
+    <t>PAC</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">수질분석 키트 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="굴림체"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>(암모니아성질소,질산성질소.인.알카리도)</t>
+    </r>
+  </si>
+  <si>
+    <t>NH3 - N</t>
+  </si>
+  <si>
+    <t>NO3 - N</t>
+  </si>
+  <si>
+    <t>PO4 - P</t>
+  </si>
+  <si>
+    <t>Alkalinity</t>
+  </si>
+  <si>
+    <t>특이사항 :</t>
+  </si>
+  <si>
+    <t>(  월)  약 품 관 리 대 장</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
+      <charset val="129"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="굴림체"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <name val="Calibri"/>
+      <color rgb="FF000000"/>
+      <name val="굴림체"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="굴림체"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="굴림체"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +222,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="24">
     <border>
       <left/>
       <right/>
@@ -48,15 +230,392 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="31">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -72,7 +631,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -82,44 +641,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="0E2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E8E8E8"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="E97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="196B24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="0F9ED5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="A02B93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="4EA72E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -147,14 +706,31 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -182,6 +758,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -193,180 +786,136 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="35000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
                 <a:shade val="100000"/>
-                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
+            <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults>
-    <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </a:style>
-    </a:spDef>
     <a:lnDef>
       <a:spPr/>
       <a:bodyPr/>
@@ -388,26 +937,204 @@
     </a:lnDef>
   </a:objectDefaults>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B78DE35D-43C7-4BE3-A125-772600B14ED5}">
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="25.5" customWidth="1"/>
+    <col min="2" max="5" width="13" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:5" ht="85.8" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A2" s="30"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+    </row>
+    <row r="3" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="30"/>
+      <c r="B3" s="30"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="30"/>
+    </row>
+    <row r="4" spans="1:5" ht="38.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A4" s="11" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="B4" s="12" t="s">
         <v>1</v>
       </c>
+      <c r="C4" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="13" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="10"/>
+    </row>
+    <row r="6" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="5"/>
+    </row>
+    <row r="7" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="5"/>
+    </row>
+    <row r="8" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="4"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="5"/>
+    </row>
+    <row r="9" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="4"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="5"/>
+    </row>
+    <row r="10" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="4"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="5"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A11" s="14"/>
+      <c r="B11" s="15"/>
+      <c r="C11" s="15"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="16"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A12" s="17"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="19"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A13" s="20"/>
+      <c r="B13" s="21"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="22"/>
+    </row>
+    <row r="14" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" s="24"/>
+      <c r="C14" s="24"/>
+      <c r="D14" s="24"/>
+      <c r="E14" s="25"/>
+    </row>
+    <row r="15" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="5"/>
+    </row>
+    <row r="16" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="5"/>
+    </row>
+    <row r="17" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="5"/>
+    </row>
+    <row r="18" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="5"/>
+    </row>
+    <row r="19" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="6"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="7"/>
+    </row>
+    <row r="20" spans="1:5" ht="72" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A20" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="B20" s="27"/>
+      <c r="C20" s="27"/>
+      <c r="D20" s="27"/>
+      <c r="E20" s="28"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <mergeCells count="6">
+    <mergeCell ref="A11:E13"/>
+    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A2:E2"/>
+  </mergeCells>
+  <phoneticPr fontId="6" type="noConversion"/>
+  <pageMargins left="0.84" right="0.7" top="1.31" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>